--- a/astro-site/public/dl/haccp-templates/10-water-quality-log.xlsx
+++ b/astro-site/public/dl/haccp-templates/10-water-quality-log.xlsx
@@ -686,7 +686,7 @@
     <row r="13">
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>▸ OK — chlorine between 0.2 and 4.0 mg/L and Normal appearance.</t>
+          <t>▸ OK — chlorine between 0.2 and 4.0 mg/L and Normal appearance. 0.2 mg/L is the entry-point minimum (measure total chlorine if your utility uses chloramine; in the distribution system a detectable residual is required).</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>▸ US: free chlorine residual 0.2-4.0 mg/L (40 CFR 141.72 and 141.65); private wells and other non-public systems: annual sampling (FDA Food Code §5-102.13). UK: Private Water Supplies Regulations 2016 for private supplies; your water company for the public supply.</t>
+          <t>▸ US: residual chlorine 0.2-4.0 mg/L, with 0.2 mg/L as the entry-point minimum (40 CFR 141.72 and 141.65; measure total chlorine if your utility uses chloramine; in the distribution system a detectable residual is required); private wells and other non-public systems: annual sampling (FDA Food Code §5-102.13). UK: Private Water Supplies Regulations 2016 for private supplies; your water company for the public supply.</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
     <row r="37" ht="12.2" customHeight="1">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>Acceptable free residual chlorine at the point of use: 0.2 - 4.0 mg/L (40 CFR 141.72 and 141.65).</t>
+          <t>Acceptable residual chlorine at the point of use: 0.2 - 4.0 mg/L, with 0.2 mg/L as the entry-point minimum (40 CFR 141.72) and 4.0 mg/L as the maximum (40 CFR 141.65). Measure total chlorine if your utility uses chloramine; in the distribution system a detectable residual is required.</t>
         </is>
       </c>
     </row>
